--- a/sample-import-en.xlsx
+++ b/sample-import-en.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ozada\apps\isletmetakip\defterappv2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CA95AD-A54B-4599-8873-CB095B43A887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75F83B9-2391-4037-B726-E0572BEC370E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="102">
   <si>
     <t>DATE</t>
   </si>
@@ -55,9 +55,6 @@
     <t>CURRENCY</t>
   </si>
   <si>
-    <t>2024-01-01 08:58</t>
-  </si>
-  <si>
     <t>SALE</t>
   </si>
   <si>
@@ -73,9 +70,6 @@
     <t>Emily Davis</t>
   </si>
   <si>
-    <t>2024-01-01 14:36</t>
-  </si>
-  <si>
     <t>INCOME</t>
   </si>
   <si>
@@ -88,9 +82,6 @@
     <t>Bank of America</t>
   </si>
   <si>
-    <t>2024-01-06 14:11</t>
-  </si>
-  <si>
     <t>PAYMENT</t>
   </si>
   <si>
@@ -103,9 +94,6 @@
     <t>Mega Market</t>
   </si>
   <si>
-    <t>2024-01-06 16:01</t>
-  </si>
-  <si>
     <t>EXPENSE</t>
   </si>
   <si>
@@ -118,24 +106,15 @@
     <t>Cash</t>
   </si>
   <si>
-    <t>2024-01-11 12:03</t>
-  </si>
-  <si>
     <t>Cleaning supplies</t>
   </si>
   <si>
     <t>INSURANCE</t>
   </si>
   <si>
-    <t>2024-01-12 18:49</t>
-  </si>
-  <si>
     <t>Consulting fee</t>
   </si>
   <si>
-    <t>2024-01-14 11:21</t>
-  </si>
-  <si>
     <t>Electric bill</t>
   </si>
   <si>
@@ -145,18 +124,12 @@
     <t>Wells Fargo</t>
   </si>
   <si>
-    <t>2024-01-15 16:28</t>
-  </si>
-  <si>
     <t>Wholesale sale</t>
   </si>
   <si>
     <t>Chris Miller</t>
   </si>
   <si>
-    <t>2024-01-15 19:23</t>
-  </si>
-  <si>
     <t>STAFF EXPENSE</t>
   </si>
   <si>
@@ -172,9 +145,6 @@
     <t>Maria Garcia</t>
   </si>
   <si>
-    <t>2024-01-18 15:29</t>
-  </si>
-  <si>
     <t>PURCHASE</t>
   </si>
   <si>
@@ -184,595 +154,178 @@
     <t>ABC Supply Co</t>
   </si>
   <si>
-    <t>2024-01-20 13:12</t>
-  </si>
-  <si>
     <t>Wire transfer sale</t>
   </si>
   <si>
-    <t>2024-01-21 16:36</t>
-  </si>
-  <si>
     <t>SERVICES</t>
   </si>
   <si>
-    <t>2024-01-25 14:25</t>
-  </si>
-  <si>
     <t>Jessica Thomas</t>
   </si>
   <si>
-    <t>2024-01-26 09:21</t>
-  </si>
-  <si>
-    <t>2024-02-02 18:51</t>
-  </si>
-  <si>
     <t>Raw material purchase</t>
   </si>
   <si>
     <t>Star Logistics</t>
   </si>
   <si>
-    <t>2024-02-03 14:25</t>
-  </si>
-  <si>
     <t>COLLECTION</t>
   </si>
   <si>
     <t>Customer collection</t>
   </si>
   <si>
-    <t>2024-02-05 11:45</t>
-  </si>
-  <si>
     <t>Office supplies</t>
   </si>
   <si>
     <t>OFFICE</t>
   </si>
   <si>
-    <t>2024-02-09 19:20</t>
-  </si>
-  <si>
     <t>Retail sale</t>
   </si>
   <si>
     <t>Michael Johnson</t>
   </si>
   <si>
-    <t>2024-02-13 11:01</t>
-  </si>
-  <si>
     <t>Stock purchase</t>
   </si>
   <si>
     <t>Trust Imports</t>
   </si>
   <si>
-    <t>2024-02-17 12:28</t>
-  </si>
-  <si>
     <t>Vehicle fuel</t>
   </si>
   <si>
     <t>ELECTRICITY</t>
   </si>
   <si>
-    <t>2024-02-18 14:13</t>
-  </si>
-  <si>
     <t>MAINTENANCE</t>
   </si>
   <si>
-    <t>2024-02-19 08:05</t>
-  </si>
-  <si>
-    <t>2024-02-25 08:40</t>
-  </si>
-  <si>
     <t>Product procurement</t>
   </si>
   <si>
     <t>XYZ Wholesale</t>
   </si>
   <si>
-    <t>2024-02-25 15:24</t>
-  </si>
-  <si>
     <t>Order delivery</t>
   </si>
   <si>
     <t>Sarah Brown</t>
   </si>
   <si>
-    <t>2024-02-26 15:54</t>
-  </si>
-  <si>
     <t>Goods purchase</t>
   </si>
   <si>
-    <t>2024-02-28 08:27</t>
-  </si>
-  <si>
     <t>Amanda Taylor</t>
   </si>
   <si>
-    <t>2024-02-29 15:42</t>
-  </si>
-  <si>
     <t>David Wilson</t>
   </si>
   <si>
-    <t>2024-03-11 13:32</t>
-  </si>
-  <si>
     <t>Credit card sale</t>
   </si>
   <si>
-    <t>2024-03-12 17:02</t>
-  </si>
-  <si>
-    <t>2024-03-15 09:36</t>
-  </si>
-  <si>
     <t>STAFF COLLECTION</t>
   </si>
   <si>
     <t>Advance return</t>
   </si>
   <si>
-    <t>2024-03-15 10:42</t>
-  </si>
-  <si>
     <t>Cash sale</t>
   </si>
   <si>
-    <t>2024-03-16 18:25</t>
-  </si>
-  <si>
-    <t>2024-03-19 12:45</t>
-  </si>
-  <si>
-    <t>2024-03-21 16:22</t>
-  </si>
-  <si>
-    <t>2024-03-24 12:03</t>
-  </si>
-  <si>
-    <t>2024-03-26 08:06</t>
-  </si>
-  <si>
-    <t>2024-03-29 15:16</t>
-  </si>
-  <si>
-    <t>2024-03-31 11:06</t>
-  </si>
-  <si>
-    <t>2024-03-31 14:34</t>
-  </si>
-  <si>
     <t>TRANSFER</t>
   </si>
   <si>
     <t>Inter-account transfer</t>
   </si>
   <si>
-    <t>2024-04-18 12:50</t>
-  </si>
-  <si>
-    <t>2024-04-19 18:33</t>
-  </si>
-  <si>
     <t>John Smith</t>
   </si>
   <si>
-    <t>2024-04-20 09:41</t>
-  </si>
-  <si>
-    <t>2024-04-20 17:40</t>
-  </si>
-  <si>
-    <t>2024-04-22 10:09</t>
-  </si>
-  <si>
     <t>Phone bill</t>
   </si>
   <si>
-    <t>2024-04-23 10:04</t>
-  </si>
-  <si>
-    <t>2024-04-26 17:10</t>
-  </si>
-  <si>
-    <t>2024-04-27 09:00</t>
-  </si>
-  <si>
     <t>Google Ads</t>
   </si>
   <si>
     <t>FUEL</t>
   </si>
   <si>
-    <t>2024-05-02 12:25</t>
-  </si>
-  <si>
     <t>Bank to cash</t>
   </si>
   <si>
-    <t>2024-05-06 10:00</t>
-  </si>
-  <si>
-    <t>2024-05-10 17:59</t>
-  </si>
-  <si>
     <t>Central Trading</t>
   </si>
   <si>
-    <t>2024-05-21 16:19</t>
-  </si>
-  <si>
     <t>Service fee</t>
   </si>
   <si>
-    <t>2024-05-24 14:57</t>
-  </si>
-  <si>
     <t>Internet bill</t>
   </si>
   <si>
     <t>RENT</t>
   </si>
   <si>
-    <t>2024-05-26 18:03</t>
-  </si>
-  <si>
     <t>Advertising expense</t>
   </si>
   <si>
-    <t>2024-05-30 16:53</t>
-  </si>
-  <si>
-    <t>2024-06-06 10:25</t>
-  </si>
-  <si>
-    <t>2024-06-07 15:38</t>
-  </si>
-  <si>
-    <t>2024-06-14 12:38</t>
-  </si>
-  <si>
-    <t>2024-06-17 10:50</t>
-  </si>
-  <si>
-    <t>2024-06-17 13:11</t>
-  </si>
-  <si>
-    <t>2024-06-22 15:16</t>
-  </si>
-  <si>
-    <t>2024-06-22 17:03</t>
-  </si>
-  <si>
-    <t>2024-06-26 11:30</t>
-  </si>
-  <si>
     <t>Lisa White</t>
   </si>
   <si>
-    <t>2024-07-02 19:28</t>
-  </si>
-  <si>
     <t>Tech Plus</t>
   </si>
   <si>
-    <t>2024-07-06 15:06</t>
-  </si>
-  <si>
-    <t>2024-07-08 17:37</t>
-  </si>
-  <si>
-    <t>2024-07-10 17:15</t>
-  </si>
-  <si>
-    <t>2024-07-15 11:37</t>
-  </si>
-  <si>
     <t>INTEREST</t>
   </si>
   <si>
-    <t>2024-07-16 15:52</t>
-  </si>
-  <si>
-    <t>2024-07-17 16:11</t>
-  </si>
-  <si>
-    <t>2024-07-21 19:46</t>
-  </si>
-  <si>
-    <t>2024-07-23 11:13</t>
-  </si>
-  <si>
-    <t>2024-07-23 11:30</t>
-  </si>
-  <si>
-    <t>2024-07-24 11:03</t>
-  </si>
-  <si>
     <t>Cash to bank</t>
   </si>
   <si>
-    <t>2024-07-28 10:56</t>
-  </si>
-  <si>
-    <t>2024-08-03 08:32</t>
-  </si>
-  <si>
     <t>James Anderson</t>
   </si>
   <si>
-    <t>2024-08-05 10:07</t>
-  </si>
-  <si>
-    <t>2024-08-07 17:53</t>
-  </si>
-  <si>
     <t>Robert Clark</t>
   </si>
   <si>
-    <t>2024-08-15 19:41</t>
-  </si>
-  <si>
     <t>INTERNET</t>
   </si>
   <si>
-    <t>2024-08-16 17:24</t>
-  </si>
-  <si>
-    <t>2024-08-19 09:03</t>
-  </si>
-  <si>
-    <t>2024-08-20 08:34</t>
-  </si>
-  <si>
-    <t>2024-08-20 10:34</t>
-  </si>
-  <si>
-    <t>2024-08-21 10:05</t>
-  </si>
-  <si>
-    <t>2024-08-22 16:44</t>
-  </si>
-  <si>
-    <t>2024-08-23 15:20</t>
-  </si>
-  <si>
-    <t>2024-08-26 17:44</t>
-  </si>
-  <si>
-    <t>2024-08-27 13:34</t>
-  </si>
-  <si>
     <t>WATER</t>
   </si>
   <si>
-    <t>2024-08-31 10:06</t>
-  </si>
-  <si>
-    <t>2024-08-31 19:20</t>
-  </si>
-  <si>
     <t>Jane Doe</t>
   </si>
   <si>
-    <t>2024-09-05 18:43</t>
-  </si>
-  <si>
-    <t>2024-09-11 13:43</t>
-  </si>
-  <si>
-    <t>2024-09-12 12:41</t>
-  </si>
-  <si>
-    <t>2024-09-17 13:00</t>
-  </si>
-  <si>
-    <t>2024-09-17 18:45</t>
-  </si>
-  <si>
-    <t>2024-09-18 18:23</t>
-  </si>
-  <si>
-    <t>2024-09-19 15:51</t>
-  </si>
-  <si>
-    <t>2024-09-19 18:08</t>
-  </si>
-  <si>
     <t>Stationery</t>
   </si>
   <si>
-    <t>2024-09-20 13:27</t>
-  </si>
-  <si>
-    <t>2024-09-23 15:09</t>
-  </si>
-  <si>
-    <t>2024-09-25 13:13</t>
-  </si>
-  <si>
-    <t>2024-09-28 17:41</t>
-  </si>
-  <si>
     <t>Salary payment</t>
   </si>
   <si>
-    <t>2024-09-29 16:00</t>
-  </si>
-  <si>
     <t>Facebook ads</t>
   </si>
   <si>
     <t>TAX</t>
   </si>
   <si>
-    <t>2024-09-30 14:30</t>
-  </si>
-  <si>
-    <t>2024-10-01 16:59</t>
-  </si>
-  <si>
-    <t>2024-10-02 10:10</t>
-  </si>
-  <si>
-    <t>2024-10-04 10:21</t>
-  </si>
-  <si>
-    <t>2024-10-04 13:02</t>
-  </si>
-  <si>
-    <t>2024-10-10 19:57</t>
-  </si>
-  <si>
-    <t>2024-10-12 11:42</t>
-  </si>
-  <si>
     <t>Kevin Lee</t>
   </si>
   <si>
-    <t>2024-10-12 19:03</t>
-  </si>
-  <si>
-    <t>2024-10-14 08:32</t>
-  </si>
-  <si>
-    <t>2024-10-15 19:43</t>
-  </si>
-  <si>
-    <t>2024-10-20 12:03</t>
-  </si>
-  <si>
-    <t>2024-10-21 08:51</t>
-  </si>
-  <si>
     <t>RENTAL INCOME</t>
   </si>
   <si>
-    <t>2024-10-23 16:46</t>
-  </si>
-  <si>
     <t>STAFF PAYMENT</t>
   </si>
   <si>
     <t>Advance payment</t>
   </si>
   <si>
-    <t>2024-10-24 09:42</t>
-  </si>
-  <si>
-    <t>2024-10-25 11:10</t>
-  </si>
-  <si>
-    <t>2024-10-28 14:52</t>
-  </si>
-  <si>
-    <t>2024-10-29 15:37</t>
-  </si>
-  <si>
-    <t>2024-11-04 17:49</t>
-  </si>
-  <si>
-    <t>2024-11-10 15:06</t>
-  </si>
-  <si>
-    <t>2024-11-12 19:00</t>
-  </si>
-  <si>
-    <t>2024-11-13 19:52</t>
-  </si>
-  <si>
-    <t>2024-11-16 12:09</t>
-  </si>
-  <si>
-    <t>2024-11-16 18:05</t>
-  </si>
-  <si>
-    <t>2024-11-19 15:34</t>
-  </si>
-  <si>
-    <t>2024-11-19 16:11</t>
-  </si>
-  <si>
-    <t>2024-11-19 19:42</t>
-  </si>
-  <si>
-    <t>2024-11-20 12:24</t>
-  </si>
-  <si>
-    <t>2024-11-22 08:34</t>
-  </si>
-  <si>
-    <t>2024-11-26 13:35</t>
-  </si>
-  <si>
-    <t>2024-11-26 16:21</t>
-  </si>
-  <si>
-    <t>2024-11-27 15:44</t>
-  </si>
-  <si>
-    <t>2024-11-30 14:24</t>
-  </si>
-  <si>
-    <t>2024-12-01 10:08</t>
-  </si>
-  <si>
-    <t>2024-12-02 12:39</t>
-  </si>
-  <si>
-    <t>2024-12-02 14:07</t>
-  </si>
-  <si>
-    <t>2024-12-05 11:21</t>
-  </si>
-  <si>
-    <t>2024-12-05 16:48</t>
-  </si>
-  <si>
-    <t>2024-12-13 17:50</t>
-  </si>
-  <si>
-    <t>2024-12-17 09:32</t>
-  </si>
-  <si>
-    <t>2024-12-17 10:09</t>
-  </si>
-  <si>
-    <t>2024-12-18 11:46</t>
-  </si>
-  <si>
-    <t>2024-12-18 14:49</t>
-  </si>
-  <si>
-    <t>2024-12-19 17:59</t>
-  </si>
-  <si>
-    <t>2024-12-23 12:25</t>
-  </si>
-  <si>
-    <t>2024-12-23 19:06</t>
-  </si>
-  <si>
-    <t>2024-12-27 17:23</t>
-  </si>
-  <si>
-    <t>2024-12-28 15:02</t>
-  </si>
-  <si>
-    <t>2024-12-29 18:14</t>
-  </si>
-  <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>2025-02-29 15:42</t>
   </si>
 </sst>
 </file>
@@ -808,8 +361,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1150,7 +704,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K151"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18.796875" customWidth="1"/>
     <col min="3" max="3" width="30.796875" customWidth="1"/>
@@ -1160,7 +714,7 @@
     <col min="11" max="11" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1195,5260 +749,5260 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>45658.373611111114</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
       <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J2">
         <v>7068</v>
       </c>
       <c r="K2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>45658.60833333333</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J3">
         <v>10918</v>
       </c>
       <c r="K3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>45663.59097222222</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" t="s">
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J4">
         <v>14064</v>
       </c>
       <c r="K4" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>45663.667361111111</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5">
         <v>648</v>
       </c>
       <c r="K5" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>32</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>45668.502083333333</v>
       </c>
       <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J6">
         <v>747</v>
       </c>
       <c r="K6" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>35</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>45669.78402777778</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J7">
         <v>14768</v>
       </c>
       <c r="K7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>37</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>45671.472916666666</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J8">
         <v>2193</v>
       </c>
       <c r="K8" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>41</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>45672.686111111114</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J9">
         <v>3955</v>
       </c>
       <c r="K9" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>44</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>45672.807638888888</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J10">
         <v>23584</v>
       </c>
       <c r="K10" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>50</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>45675.645138888889</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="H11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J11">
         <v>37634</v>
       </c>
       <c r="K11" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>54</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>45677.55</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J12">
         <v>7103</v>
       </c>
       <c r="K12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>56</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>45678.691666666666</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J13">
         <v>1735</v>
       </c>
       <c r="K13" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>58</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>45682.600694444445</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="I14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J14">
         <v>26898</v>
       </c>
       <c r="K14" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>60</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>45683.38958333333</v>
       </c>
       <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
         <v>23</v>
       </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" t="s">
-        <v>26</v>
-      </c>
       <c r="H15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J15">
         <v>20686</v>
       </c>
       <c r="K15" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>61</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>45690.785416666666</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J16">
         <v>28483</v>
       </c>
       <c r="K16" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>64</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>45691.600694444445</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" t="s">
         <v>15</v>
       </c>
-      <c r="E17" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" t="s">
-        <v>16</v>
-      </c>
       <c r="I17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J17">
         <v>5640</v>
       </c>
       <c r="K17" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>67</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>45693.489583333336</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J18">
         <v>842</v>
       </c>
       <c r="K18" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>70</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>45697.805555555555</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H19" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="I19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J19">
         <v>24406</v>
       </c>
       <c r="K19" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>73</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>45701.459027777775</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="H20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J20">
         <v>9527</v>
       </c>
       <c r="K20" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>76</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>45705.519444444442</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J21">
         <v>1039</v>
       </c>
       <c r="K21" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>79</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>45706.592361111114</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J22">
         <v>2681</v>
       </c>
       <c r="K22" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>81</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>45707.336805555555</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J23">
         <v>25369</v>
       </c>
       <c r="K23" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>82</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>45713.361111111109</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="H24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J24">
         <v>32042</v>
       </c>
       <c r="K24" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>85</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>45713.64166666667</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H25" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="I25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J25">
         <v>3912</v>
       </c>
       <c r="K25" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>88</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>45714.662499999999</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="D26" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="H26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J26">
         <v>6159</v>
       </c>
       <c r="K26" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>90</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>45716.352083333331</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H27" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="I27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J27">
         <v>18856</v>
       </c>
       <c r="K27" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H28" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J28">
         <v>13559</v>
       </c>
       <c r="K28" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>94</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>45727.563888888886</v>
       </c>
       <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" t="s">
         <v>18</v>
       </c>
-      <c r="C29" t="s">
-        <v>95</v>
-      </c>
-      <c r="D29" t="s">
-        <v>20</v>
-      </c>
       <c r="E29" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J29">
         <v>7309</v>
       </c>
       <c r="K29" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>96</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>45728.709722222222</v>
       </c>
       <c r="B30" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="H30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J30">
         <v>18123</v>
       </c>
       <c r="K30" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>97</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>45731.4</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E31" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J31">
         <v>2676</v>
       </c>
       <c r="K31" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>100</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>45731.445833333331</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="D32" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E32" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J32">
         <v>9655</v>
       </c>
       <c r="K32" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>102</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>45732.767361111109</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E33" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H33" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J33">
         <v>7350</v>
       </c>
       <c r="K33" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>103</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>45735.53125</v>
       </c>
       <c r="B34" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J34">
         <v>811</v>
       </c>
       <c r="K34" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>104</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>45737.681944444441</v>
       </c>
       <c r="B35" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C35" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E35" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="H35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J35">
         <v>24764</v>
       </c>
       <c r="K35" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>105</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>45740.502083333333</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H36" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J36">
         <v>10959</v>
       </c>
       <c r="K36" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>106</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>45742.337500000001</v>
       </c>
       <c r="B37" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" t="s">
         <v>15</v>
       </c>
-      <c r="E37" t="s">
-        <v>21</v>
-      </c>
-      <c r="F37" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" t="s">
-        <v>15</v>
-      </c>
-      <c r="H37" t="s">
-        <v>16</v>
-      </c>
       <c r="I37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J37">
         <v>18226</v>
       </c>
       <c r="K37" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>107</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>45745.636111111111</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E38" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" t="s">
         <v>15</v>
       </c>
-      <c r="F38" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" t="s">
-        <v>15</v>
-      </c>
-      <c r="H38" t="s">
-        <v>16</v>
-      </c>
       <c r="I38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J38">
         <v>14504</v>
       </c>
       <c r="K38" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>108</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>45747.462500000001</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C39" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E39" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="H39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J39">
         <v>19345</v>
       </c>
       <c r="K39" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>109</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>45747.606944444444</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C40" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="D40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E40" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I40" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="J40">
         <v>14653</v>
       </c>
       <c r="K40" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>112</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>45765.534722222219</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D41" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E41" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J41">
         <v>8316</v>
       </c>
       <c r="K41" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>113</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>45766.772916666669</v>
       </c>
       <c r="B42" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E42" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H42" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="I42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J42">
         <v>13077</v>
       </c>
       <c r="K42" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>115</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>45767.40347222222</v>
       </c>
       <c r="B43" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E43" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J43">
         <v>3831</v>
       </c>
       <c r="K43" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>116</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>45767.736111111109</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C44" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D44" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E44" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J44">
         <v>1612</v>
       </c>
       <c r="K44" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>117</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>45769.42291666667</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C45" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="D45" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E45" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J45">
         <v>2490</v>
       </c>
       <c r="K45" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>119</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>45770.419444444444</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E46" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H46" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="I46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J46">
         <v>8937</v>
       </c>
       <c r="K46" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>120</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>45773.715277777781</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="D47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J47">
         <v>5976</v>
       </c>
       <c r="K47" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>121</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>45774.375</v>
       </c>
       <c r="B48" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C48" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="D48" t="s">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="E48" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J48">
         <v>460</v>
       </c>
       <c r="K48" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>124</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>45779.517361111109</v>
       </c>
       <c r="B49" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C49" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="D49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E49" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I49" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J49">
         <v>7147</v>
       </c>
       <c r="K49" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>126</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>45783.416666666664</v>
       </c>
       <c r="B50" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" t="s">
         <v>12</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>13</v>
       </c>
-      <c r="D50" t="s">
-        <v>14</v>
-      </c>
       <c r="E50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H50" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="I50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J50">
         <v>3651</v>
       </c>
       <c r="K50" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>127</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>45787.749305555553</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C51" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="D51" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G51" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J51">
         <v>6250</v>
       </c>
       <c r="K51" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>129</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>45798.679861111108</v>
       </c>
       <c r="B52" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="D52" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E52" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J52">
         <v>14929</v>
       </c>
       <c r="K52" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>131</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>45801.622916666667</v>
       </c>
       <c r="B53" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C53" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="D53" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E53" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J53">
         <v>4608</v>
       </c>
       <c r="K53" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>134</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>45803.752083333333</v>
       </c>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="D54" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E54" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J54">
         <v>2134</v>
       </c>
       <c r="K54" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>136</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>45807.703472222223</v>
       </c>
       <c r="B55" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" t="s">
         <v>28</v>
       </c>
-      <c r="C55" t="s">
-        <v>33</v>
-      </c>
       <c r="D55" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E55" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J55">
         <v>428</v>
       </c>
       <c r="K55" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>137</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>45814.434027777781</v>
       </c>
       <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="s">
+        <v>70</v>
+      </c>
+      <c r="D56" t="s">
         <v>18</v>
       </c>
-      <c r="C56" t="s">
-        <v>101</v>
-      </c>
-      <c r="D56" t="s">
-        <v>20</v>
-      </c>
       <c r="E56" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J56">
         <v>2352</v>
       </c>
       <c r="K56" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>138</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>45815.651388888888</v>
       </c>
       <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" t="s">
         <v>18</v>
       </c>
-      <c r="C57" t="s">
+      <c r="E57" t="s">
         <v>19</v>
       </c>
-      <c r="D57" t="s">
-        <v>20</v>
-      </c>
-      <c r="E57" t="s">
-        <v>21</v>
-      </c>
       <c r="F57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J57">
         <v>6858</v>
       </c>
       <c r="K57" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>139</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>45822.526388888888</v>
       </c>
       <c r="B58" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D58" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E58" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J58">
         <v>9660</v>
       </c>
       <c r="K58" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>140</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>45825.451388888891</v>
       </c>
       <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" t="s">
         <v>18</v>
       </c>
-      <c r="C59" t="s">
-        <v>19</v>
-      </c>
-      <c r="D59" t="s">
-        <v>20</v>
-      </c>
       <c r="E59" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J59">
         <v>1144</v>
       </c>
       <c r="K59" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>141</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>45825.549305555556</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C60" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E60" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" t="s">
+        <v>14</v>
+      </c>
+      <c r="H60" t="s">
         <v>15</v>
       </c>
-      <c r="F60" t="s">
-        <v>15</v>
-      </c>
-      <c r="G60" t="s">
-        <v>15</v>
-      </c>
-      <c r="H60" t="s">
-        <v>16</v>
-      </c>
       <c r="I60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J60">
         <v>8652</v>
       </c>
       <c r="K60" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>142</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>45830.636111111111</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C61" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="D61" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E61" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J61">
         <v>2752</v>
       </c>
       <c r="K61" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>143</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>45830.710416666669</v>
       </c>
       <c r="B62" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="D62" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E62" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J62">
         <v>2104</v>
       </c>
       <c r="K62" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>144</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>45834.479166666664</v>
       </c>
       <c r="B63" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C63" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D63" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E63" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F63" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="G63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J63">
         <v>16446</v>
       </c>
       <c r="K63" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>146</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>45840.811111111114</v>
       </c>
       <c r="B64" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C64" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="D64" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G64" t="s">
-        <v>147</v>
+        <v>84</v>
       </c>
       <c r="H64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J64">
         <v>22297</v>
       </c>
       <c r="K64" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>148</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>45844.629166666666</v>
       </c>
       <c r="B65" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65" t="s">
+        <v>21</v>
+      </c>
+      <c r="D65" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65" t="s">
+        <v>14</v>
+      </c>
+      <c r="G65" t="s">
         <v>23</v>
       </c>
-      <c r="C65" t="s">
-        <v>24</v>
-      </c>
-      <c r="D65" t="s">
-        <v>15</v>
-      </c>
-      <c r="E65" t="s">
-        <v>31</v>
-      </c>
-      <c r="F65" t="s">
-        <v>15</v>
-      </c>
-      <c r="G65" t="s">
-        <v>26</v>
-      </c>
       <c r="H65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J65">
         <v>10003</v>
       </c>
       <c r="K65" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>149</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>45846.734027777777</v>
       </c>
       <c r="B66" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C66" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="D66" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H66" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="I66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J66">
         <v>15732</v>
       </c>
       <c r="K66" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>150</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>45848.71875</v>
       </c>
       <c r="B67" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C67" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D67" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G67" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J67">
         <v>18739</v>
       </c>
       <c r="K67" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>151</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>45853.484027777777</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C68" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="D68" t="s">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="E68" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J68">
         <v>9617</v>
       </c>
       <c r="K68" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>153</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>45854.661111111112</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C69" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="D69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E69" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F69" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G69" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H69" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I69" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J69">
         <v>7066</v>
       </c>
       <c r="K69" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>154</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>45855.674305555556</v>
       </c>
       <c r="B70" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C70" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="D70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H70" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J70">
         <v>27478</v>
       </c>
       <c r="K70" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>155</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>45859.823611111111</v>
       </c>
       <c r="B71" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C71" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="D71" t="s">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="E71" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J71">
         <v>12166</v>
       </c>
       <c r="K71" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>156</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>45861.467361111114</v>
       </c>
       <c r="B72" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C72" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D72" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E72" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F72" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G72" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="H72" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I72" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J72">
         <v>21280</v>
       </c>
       <c r="K72" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>157</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>45861.479166666664</v>
       </c>
       <c r="B73" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C73" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" t="s">
+        <v>85</v>
+      </c>
+      <c r="E73" t="s">
         <v>19</v>
       </c>
-      <c r="D73" t="s">
-        <v>152</v>
-      </c>
-      <c r="E73" t="s">
-        <v>21</v>
-      </c>
       <c r="F73" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G73" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H73" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I73" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J73">
         <v>8797</v>
       </c>
       <c r="K73" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>158</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>45862.460416666669</v>
       </c>
       <c r="B74" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C74" t="s">
-        <v>159</v>
+        <v>86</v>
       </c>
       <c r="D74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E74" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I74" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="J74">
         <v>9855</v>
       </c>
       <c r="K74" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>160</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>45866.455555555556</v>
       </c>
       <c r="B75" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C75" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D75" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E75" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F75" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G75" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H75" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I75" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J75">
         <v>2277</v>
       </c>
       <c r="K75" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>161</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>45872.355555555558</v>
       </c>
       <c r="B76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C76" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E76" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F76" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G76" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H76" t="s">
-        <v>162</v>
+        <v>87</v>
       </c>
       <c r="I76" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J76">
         <v>29214</v>
       </c>
       <c r="K76" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>163</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>45874.421527777777</v>
       </c>
       <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="s">
+        <v>44</v>
+      </c>
+      <c r="D77" t="s">
         <v>18</v>
       </c>
-      <c r="C77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D77" t="s">
-        <v>20</v>
-      </c>
       <c r="E77" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F77" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G77" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H77" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I77" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J77">
         <v>2258</v>
       </c>
       <c r="K77" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>164</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>45876.745138888888</v>
       </c>
       <c r="B78" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C78" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D78" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E78" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F78" t="s">
-        <v>165</v>
+        <v>88</v>
       </c>
       <c r="G78" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H78" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I78" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J78">
         <v>31545</v>
       </c>
       <c r="K78" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>166</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>45884.820138888892</v>
       </c>
       <c r="B79" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C79" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="D79" t="s">
-        <v>167</v>
+        <v>89</v>
       </c>
       <c r="E79" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F79" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G79" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H79" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I79" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J79">
         <v>1688</v>
       </c>
       <c r="K79" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>168</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>45885.724999999999</v>
       </c>
       <c r="B80" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C80" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D80" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E80" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F80" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G80" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H80" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I80" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J80">
         <v>12484</v>
       </c>
       <c r="K80" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>169</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>45888.377083333333</v>
       </c>
       <c r="B81" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C81" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="D81" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E81" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F81" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G81" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="H81" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I81" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J81">
         <v>12310</v>
       </c>
       <c r="K81" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>170</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>45889.356944444444</v>
       </c>
       <c r="B82" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C82" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D82" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E82" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F82" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G82" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H82" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I82" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J82">
         <v>12955</v>
       </c>
       <c r="K82" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>171</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>45889.44027777778</v>
       </c>
       <c r="B83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D83" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H83" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="I83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J83">
         <v>2433</v>
       </c>
       <c r="K83" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>172</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>45890.420138888891</v>
       </c>
       <c r="B84" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C84" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D84" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G84" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J84">
         <v>8548</v>
       </c>
       <c r="K84" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>173</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>45891.697222222225</v>
       </c>
       <c r="B85" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C85" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D85" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E85" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F85" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="H85" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I85" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J85">
         <v>37331</v>
       </c>
       <c r="K85" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>174</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>45892.638888888891</v>
       </c>
       <c r="B86" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C86" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D86" t="s">
-        <v>167</v>
+        <v>89</v>
       </c>
       <c r="E86" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J86">
         <v>4058</v>
       </c>
       <c r="K86" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>175</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>45895.738888888889</v>
       </c>
       <c r="B87" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C87" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D87" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E87" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F87" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G87" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="H87" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I87" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J87">
         <v>48821</v>
       </c>
       <c r="K87" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>176</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>45896.56527777778</v>
       </c>
       <c r="B88" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C88" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="D88" t="s">
-        <v>177</v>
+        <v>90</v>
       </c>
       <c r="E88" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F88" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G88" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H88" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I88" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J88">
         <v>3475</v>
       </c>
       <c r="K88" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>178</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>45900.42083333333</v>
       </c>
       <c r="B89" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C89" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D89" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E89" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F89" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G89" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H89" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I89" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J89">
         <v>3416</v>
       </c>
       <c r="K89" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>179</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>45900.805555555555</v>
       </c>
       <c r="B90" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C90" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="D90" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E90" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F90" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G90" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H90" t="s">
-        <v>180</v>
+        <v>91</v>
       </c>
       <c r="I90" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J90">
         <v>2620</v>
       </c>
       <c r="K90" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>181</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>45905.779861111114</v>
       </c>
       <c r="B91" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C91" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D91" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E91" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F91" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G91" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H91" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I91" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J91">
         <v>10163</v>
       </c>
       <c r="K91" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>182</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>45911.571527777778</v>
       </c>
       <c r="B92" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C92" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D92" t="s">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="E92" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F92" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G92" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H92" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I92" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J92">
         <v>4495</v>
       </c>
       <c r="K92" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>183</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>45912.52847222222</v>
       </c>
       <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93" t="s">
         <v>18</v>
       </c>
-      <c r="C93" t="s">
-        <v>19</v>
-      </c>
-      <c r="D93" t="s">
-        <v>20</v>
-      </c>
       <c r="E93" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F93" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G93" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H93" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I93" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J93">
         <v>5780</v>
       </c>
       <c r="K93" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>184</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>45917.541666666664</v>
       </c>
       <c r="B94" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C94" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="D94" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E94" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F94" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G94" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H94" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I94" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J94">
         <v>258</v>
       </c>
       <c r="K94" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>185</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>45917.78125</v>
       </c>
       <c r="B95" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C95" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D95" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E95" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F95" t="s">
-        <v>165</v>
+        <v>88</v>
       </c>
       <c r="G95" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H95" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I95" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J95">
         <v>15189</v>
       </c>
       <c r="K95" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>186</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>45918.765972222223</v>
       </c>
       <c r="B96" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C96" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D96" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E96" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F96" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G96" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H96" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="I96" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J96">
         <v>11350</v>
       </c>
       <c r="K96" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>187</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>45919.660416666666</v>
       </c>
       <c r="B97" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C97" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D97" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E97" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F97" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="G97" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H97" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I97" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J97">
         <v>19628</v>
       </c>
       <c r="K97" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>188</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>45919.755555555559</v>
       </c>
       <c r="B98" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C98" t="s">
-        <v>189</v>
+        <v>92</v>
       </c>
       <c r="D98" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E98" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J98">
         <v>1437</v>
       </c>
       <c r="K98" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>190</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>45920.560416666667</v>
       </c>
       <c r="B99" t="s">
+        <v>11</v>
+      </c>
+      <c r="C99" t="s">
         <v>12</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>13</v>
       </c>
-      <c r="D99" t="s">
-        <v>14</v>
-      </c>
       <c r="E99" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F99" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G99" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H99" t="s">
-        <v>162</v>
+        <v>87</v>
       </c>
       <c r="I99" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J99">
         <v>27683</v>
       </c>
       <c r="K99" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>191</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>45923.631249999999</v>
       </c>
       <c r="B100" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C100" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D100" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E100" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F100" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G100" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H100" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I100" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J100">
         <v>11761</v>
       </c>
       <c r="K100" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>192</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>45925.550694444442</v>
       </c>
       <c r="B101" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C101" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="D101" t="s">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="E101" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F101" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G101" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H101" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I101" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J101">
         <v>4840</v>
       </c>
       <c r="K101" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>193</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>45928.736805555556</v>
       </c>
       <c r="B102" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C102" t="s">
-        <v>194</v>
+        <v>93</v>
       </c>
       <c r="D102" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E102" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F102" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="G102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J102">
         <v>31586</v>
       </c>
       <c r="K102" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>195</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>45929.666666666664</v>
       </c>
       <c r="B103" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C103" t="s">
-        <v>196</v>
+        <v>94</v>
       </c>
       <c r="D103" t="s">
-        <v>197</v>
+        <v>95</v>
       </c>
       <c r="E103" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F103" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G103" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H103" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I103" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J103">
         <v>3585</v>
       </c>
       <c r="K103" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>198</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>45930.604166666664</v>
       </c>
       <c r="B104" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C104" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D104" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E104" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F104" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G104" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H104" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I104" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J104">
         <v>2176</v>
       </c>
       <c r="K104" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>199</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>45931.707638888889</v>
       </c>
       <c r="B105" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C105" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D105" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E105" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F105" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G105" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H105" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I105" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J105">
         <v>206</v>
       </c>
       <c r="K105" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>200</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>45932.423611111109</v>
       </c>
       <c r="B106" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C106" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D106" t="s">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="E106" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F106" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G106" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H106" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I106" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J106">
         <v>8313</v>
       </c>
       <c r="K106" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>201</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>45934.431250000001</v>
       </c>
       <c r="B107" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C107" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D107" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E107" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F107" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G107" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="H107" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I107" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J107">
         <v>42211</v>
       </c>
       <c r="K107" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>202</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>45934.543055555558</v>
       </c>
       <c r="B108" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C108" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D108" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E108" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F108" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G108" t="s">
-        <v>147</v>
+        <v>84</v>
       </c>
       <c r="H108" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I108" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J108">
         <v>3930</v>
       </c>
       <c r="K108" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>203</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>45940.831250000003</v>
       </c>
       <c r="B109" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C109" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D109" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E109" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F109" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G109" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="H109" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I109" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J109">
         <v>3720</v>
       </c>
       <c r="K109" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>204</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>45942.487500000003</v>
       </c>
       <c r="B110" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="C110" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="D110" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E110" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F110" t="s">
-        <v>205</v>
+        <v>96</v>
       </c>
       <c r="G110" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H110" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I110" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J110">
         <v>2440</v>
       </c>
       <c r="K110" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>206</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>45942.793749999997</v>
       </c>
       <c r="B111" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C111" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D111" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E111" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F111" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G111" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="H111" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I111" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J111">
         <v>19962</v>
       </c>
       <c r="K111" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>207</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>45944.355555555558</v>
       </c>
       <c r="B112" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C112" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D112" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E112" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F112" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G112" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H112" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="I112" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J112">
         <v>15543</v>
       </c>
       <c r="K112" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>208</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>45945.821527777778</v>
       </c>
       <c r="B113" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C113" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D113" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E113" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F113" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G113" t="s">
-        <v>147</v>
+        <v>84</v>
       </c>
       <c r="H113" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I113" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J113">
         <v>9573</v>
       </c>
       <c r="K113" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>209</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>45950.502083333333</v>
       </c>
       <c r="B114" t="s">
+        <v>11</v>
+      </c>
+      <c r="C114" t="s">
         <v>12</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
         <v>13</v>
       </c>
-      <c r="D114" t="s">
-        <v>14</v>
-      </c>
       <c r="E114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H114" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="I114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J114">
         <v>11653</v>
       </c>
       <c r="K114" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>210</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>45951.368750000001</v>
       </c>
       <c r="B115" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C115" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D115" t="s">
-        <v>211</v>
+        <v>97</v>
       </c>
       <c r="E115" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F115" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G115" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H115" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I115" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J115">
         <v>6970</v>
       </c>
       <c r="K115" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>212</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>45953.698611111111</v>
       </c>
       <c r="B116" t="s">
-        <v>213</v>
+        <v>98</v>
       </c>
       <c r="C116" t="s">
-        <v>214</v>
+        <v>99</v>
       </c>
       <c r="D116" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E116" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F116" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="G116" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H116" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I116" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J116">
         <v>2753</v>
       </c>
       <c r="K116" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>215</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>45954.404166666667</v>
       </c>
       <c r="B117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C117" t="s">
         <v>28</v>
       </c>
-      <c r="C117" t="s">
-        <v>33</v>
-      </c>
       <c r="D117" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E117" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F117" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G117" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H117" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I117" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J117">
         <v>4495</v>
       </c>
       <c r="K117" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>216</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>45955.465277777781</v>
       </c>
       <c r="B118" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C118" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D118" t="s">
-        <v>211</v>
+        <v>97</v>
       </c>
       <c r="E118" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F118" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G118" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H118" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I118" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J118">
         <v>1764</v>
       </c>
       <c r="K118" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>217</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>45958.619444444441</v>
       </c>
       <c r="B119" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C119" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D119" t="s">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="E119" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F119" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G119" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H119" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I119" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J119">
         <v>1081</v>
       </c>
       <c r="K119" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>218</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>45959.650694444441</v>
       </c>
       <c r="B120" t="s">
+        <v>11</v>
+      </c>
+      <c r="C120" t="s">
         <v>12</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
         <v>13</v>
       </c>
-      <c r="D120" t="s">
-        <v>14</v>
-      </c>
       <c r="E120" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F120" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G120" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H120" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I120" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J120">
         <v>10366</v>
       </c>
       <c r="K120" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>219</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>45965.742361111108</v>
       </c>
       <c r="B121" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C121" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D121" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E121" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F121" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G121" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="H121" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I121" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J121">
         <v>34838</v>
       </c>
       <c r="K121" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>220</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>45971.629166666666</v>
       </c>
       <c r="B122" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C122" t="s">
-        <v>189</v>
+        <v>92</v>
       </c>
       <c r="D122" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="E122" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F122" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G122" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H122" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I122" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J122">
         <v>2101</v>
       </c>
       <c r="K122" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>221</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>45973.791666666664</v>
       </c>
       <c r="B123" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C123" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D123" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E123" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F123" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G123" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H123" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I123" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J123">
         <v>5539</v>
       </c>
       <c r="K123" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>222</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>45974.827777777777</v>
       </c>
       <c r="B124" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C124" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="D124" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E124" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F124" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G124" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H124" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I124" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J124">
         <v>4313</v>
       </c>
       <c r="K124" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>223</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>45977.506249999999</v>
       </c>
       <c r="B125" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C125" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D125" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E125" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F125" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G125" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H125" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I125" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J125">
         <v>43038</v>
       </c>
       <c r="K125" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>224</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>45977.753472222219</v>
       </c>
       <c r="B126" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C126" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E126" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F126" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G126" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H126" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I126" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J126">
         <v>6075</v>
       </c>
       <c r="K126" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>225</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>45980.648611111108</v>
       </c>
       <c r="B127" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C127" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D127" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E127" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F127" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G127" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H127" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I127" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J127">
         <v>4960</v>
       </c>
       <c r="K127" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>226</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>45980.674305555556</v>
       </c>
       <c r="B128" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C128" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D128" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E128" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F128" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G128" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H128" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="I128" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J128">
         <v>8869</v>
       </c>
       <c r="K128" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>227</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>45980.820833333331</v>
       </c>
       <c r="B129" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C129" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D129" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E129" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F129" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G129" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="H129" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I129" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J129">
         <v>19939</v>
       </c>
       <c r="K129" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>228</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>45981.51666666667</v>
       </c>
       <c r="B130" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C130" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D130" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E130" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F130" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G130" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="H130" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I130" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J130">
         <v>18883</v>
       </c>
       <c r="K130" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>229</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>45983.356944444444</v>
       </c>
       <c r="B131" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C131" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="D131" t="s">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="E131" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F131" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G131" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H131" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I131" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J131">
         <v>8803</v>
       </c>
       <c r="K131" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>230</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>45987.565972222219</v>
       </c>
       <c r="B132" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C132" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D132" t="s">
-        <v>177</v>
+        <v>90</v>
       </c>
       <c r="E132" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F132" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G132" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H132" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I132" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J132">
         <v>3576</v>
       </c>
       <c r="K132" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>231</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>45987.681250000001</v>
       </c>
       <c r="B133" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C133" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="D133" t="s">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="E133" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F133" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G133" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H133" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I133" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J133">
         <v>3830</v>
       </c>
       <c r="K133" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>232</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>45988.655555555553</v>
       </c>
       <c r="B134" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C134" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D134" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E134" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F134" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G134" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H134" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I134" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J134">
         <v>587</v>
       </c>
       <c r="K134" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>233</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>45991.6</v>
       </c>
       <c r="B135" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C135" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="D135" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E135" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F135" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G135" t="s">
-        <v>147</v>
+        <v>84</v>
       </c>
       <c r="H135" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I135" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J135">
         <v>5957</v>
       </c>
       <c r="K135" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>234</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>45992.422222222223</v>
       </c>
       <c r="B136" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C136" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="D136" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E136" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F136" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G136" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H136" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I136" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J136">
         <v>10952</v>
       </c>
       <c r="K136" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>235</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>45993.527083333334</v>
       </c>
       <c r="B137" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C137" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="D137" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E137" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F137" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G137" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="H137" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I137" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J137">
         <v>16335</v>
       </c>
       <c r="K137" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>236</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>45993.588194444441</v>
       </c>
       <c r="B138" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C138" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D138" t="s">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="E138" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F138" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G138" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H138" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I138" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J138">
         <v>9826</v>
       </c>
       <c r="K138" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>237</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>45996.472916666666</v>
       </c>
       <c r="B139" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C139" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="D139" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E139" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F139" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G139" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H139" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I139" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J139">
         <v>2437</v>
       </c>
       <c r="K139" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>238</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>45996.7</v>
       </c>
       <c r="B140" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140" t="s">
         <v>12</v>
       </c>
-      <c r="C140" t="s">
+      <c r="D140" t="s">
         <v>13</v>
       </c>
-      <c r="D140" t="s">
-        <v>14</v>
-      </c>
       <c r="E140" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F140" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G140" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H140" t="s">
-        <v>180</v>
+        <v>91</v>
       </c>
       <c r="I140" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J140">
         <v>16288</v>
       </c>
       <c r="K140" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="141" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
-        <v>239</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>46004.743055555555</v>
       </c>
       <c r="B141" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C141" t="s">
-        <v>159</v>
+        <v>86</v>
       </c>
       <c r="D141" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E141" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F141" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G141" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H141" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I141" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J141">
         <v>10138</v>
       </c>
       <c r="K141" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
-        <v>240</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
+        <v>46008.397222222222</v>
       </c>
       <c r="B142" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C142" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="D142" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E142" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F142" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G142" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H142" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I142" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J142">
         <v>8839</v>
       </c>
       <c r="K142" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="143" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>241</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
+        <v>46008.42291666667</v>
       </c>
       <c r="B143" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C143" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="D143" t="s">
-        <v>211</v>
+        <v>97</v>
       </c>
       <c r="E143" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F143" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G143" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H143" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I143" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J143">
         <v>11535</v>
       </c>
       <c r="K143" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>242</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A144" s="1">
+        <v>46009.490277777775</v>
       </c>
       <c r="B144" t="s">
+        <v>20</v>
+      </c>
+      <c r="C144" t="s">
+        <v>21</v>
+      </c>
+      <c r="D144" t="s">
+        <v>14</v>
+      </c>
+      <c r="E144" t="s">
+        <v>33</v>
+      </c>
+      <c r="F144" t="s">
+        <v>14</v>
+      </c>
+      <c r="G144" t="s">
         <v>23</v>
       </c>
-      <c r="C144" t="s">
-        <v>24</v>
-      </c>
-      <c r="D144" t="s">
-        <v>15</v>
-      </c>
-      <c r="E144" t="s">
-        <v>40</v>
-      </c>
-      <c r="F144" t="s">
-        <v>15</v>
-      </c>
-      <c r="G144" t="s">
-        <v>26</v>
-      </c>
       <c r="H144" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I144" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J144">
         <v>19691</v>
       </c>
       <c r="K144" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
-        <v>243</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A145" s="1">
+        <v>46009.617361111108</v>
       </c>
       <c r="B145" t="s">
+        <v>11</v>
+      </c>
+      <c r="C145" t="s">
         <v>12</v>
       </c>
-      <c r="C145" t="s">
+      <c r="D145" t="s">
         <v>13</v>
       </c>
-      <c r="D145" t="s">
-        <v>14</v>
-      </c>
       <c r="E145" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F145" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G145" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H145" t="s">
-        <v>162</v>
+        <v>87</v>
       </c>
       <c r="I145" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J145">
         <v>27211</v>
       </c>
       <c r="K145" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
-        <v>244</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>46010.749305555553</v>
       </c>
       <c r="B146" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C146" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="E146" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F146" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G146" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H146" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I146" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J146">
         <v>5755</v>
       </c>
       <c r="K146" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
-        <v>245</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>46014.517361111109</v>
       </c>
       <c r="B147" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C147" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D147" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E147" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F147" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G147" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H147" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I147" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J147">
         <v>40524</v>
       </c>
       <c r="K147" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>246</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>46014.79583333333</v>
       </c>
       <c r="B148" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C148" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D148" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H148" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="I148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J148">
         <v>22054</v>
       </c>
       <c r="K148" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
-        <v>247</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>46018.724305555559</v>
       </c>
       <c r="B149" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149" t="s">
         <v>12</v>
       </c>
-      <c r="C149" t="s">
+      <c r="D149" t="s">
         <v>13</v>
       </c>
-      <c r="D149" t="s">
-        <v>14</v>
-      </c>
       <c r="E149" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F149" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G149" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H149" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="I149" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J149">
         <v>19512</v>
       </c>
       <c r="K149" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>248</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>46019.626388888886</v>
       </c>
       <c r="B150" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C150" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D150" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E150" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F150" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G150" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H150" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I150" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J150">
         <v>611</v>
       </c>
       <c r="K150" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>249</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>46020.759722222225</v>
       </c>
       <c r="B151" t="s">
-        <v>213</v>
+        <v>98</v>
       </c>
       <c r="C151" t="s">
-        <v>214</v>
+        <v>99</v>
       </c>
       <c r="D151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E151" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F151" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="G151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J151">
         <v>4983</v>
       </c>
       <c r="K151" t="s">
-        <v>250</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K1 A3:J151 A2:J2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:K1 B151:J151 B2:J2 B3:J3 B4:J4 B5:J5 B6:J6 B7:J7 B8:J8 B9:J9 B10:J10 B11:J11 B12:J12 B13:J13 B14:J14 B15:J15 B16:J16 B17:J17 B18:J18 B19:J19 B20:J20 B21:J21 B22:J22 B23:J23 B24:J24 B25:J25 B26:J26 B27:J27 B28:J28 B29:J29 B30:J30 B31:J31 B32:J32 B33:J33 B34:J34 B35:J35 B36:J36 B37:J37 B38:J38 B39:J39 B40:J40 B41:J41 B42:J42 B43:J43 B44:J44 B45:J45 B46:J46 B47:J47 B48:J48 B49:J49 B50:J50 B51:J51 B52:J52 B53:J53 B54:J54 B55:J55 B56:J56 B57:J57 B58:J58 B59:J59 B60:J60 B61:J61 B62:J62 B63:J63 B64:J64 B65:J65 B66:J66 B67:J67 B68:J68 B69:J69 B70:J70 B71:J71 B72:J72 B73:J73 B74:J74 B75:J75 B76:J76 B77:J77 B78:J78 B79:J79 B80:J80 B81:J81 B82:J82 B83:J83 B84:J84 B85:J85 B86:J86 B87:J87 B88:J88 B89:J89 B90:J90 B91:J91 B92:J92 B93:J93 B94:J94 B95:J95 B96:J96 B97:J97 B98:J98 B99:J99 B100:J100 B101:J101 B102:J102 B103:J103 B104:J104 B105:J105 B106:J106 B107:J107 B108:J108 B109:J109 B110:J110 B111:J111 B112:J112 B113:J113 B114:J114 B115:J115 B116:J116 B117:J117 B118:J118 B119:J119 B120:J120 B121:J121 B122:J122 B123:J123 B124:J124 B125:J125 B126:J126 B127:J127 B128:J128 B129:J129 B130:J130 B131:J131 B132:J132 B133:J133 B134:J134 B135:J135 B136:J136 B137:J137 B138:J138 B139:J139 B140:J140 B141:J141 B142:J142 B143:J143 B144:J144 B145:J145 B146:J146 B147:J147 B148:J148 B149:J149 B150:J150" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>